--- a/artfynd/A 43291-2024 artfynd.xlsx
+++ b/artfynd/A 43291-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120282395</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78661</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>120282414</v>
       </c>
       <c r="B3" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43291-2024 artfynd.xlsx
+++ b/artfynd/A 43291-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120282395</v>
+        <v>120282414</v>
       </c>
       <c r="B2" t="n">
-        <v>78661</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1036</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615802</v>
+        <v>615784</v>
       </c>
       <c r="R2" t="n">
         <v>6560219</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120282414</v>
+        <v>120282395</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>78661</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1036</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615784</v>
+        <v>615802</v>
       </c>
       <c r="R3" t="n">
         <v>6560219</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43291-2024 artfynd.xlsx
+++ b/artfynd/A 43291-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120282414</v>
+        <v>120282395</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>78661</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1036</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615784</v>
+        <v>615802</v>
       </c>
       <c r="R2" t="n">
         <v>6560219</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120282395</v>
+        <v>120282414</v>
       </c>
       <c r="B3" t="n">
-        <v>78661</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1036</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615802</v>
+        <v>615784</v>
       </c>
       <c r="R3" t="n">
         <v>6560219</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43291-2024 artfynd.xlsx
+++ b/artfynd/A 43291-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120282395</v>
+        <v>120282414</v>
       </c>
       <c r="B2" t="n">
-        <v>78661</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1036</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615802</v>
+        <v>615784</v>
       </c>
       <c r="R2" t="n">
         <v>6560219</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120282414</v>
+        <v>120282395</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>78661</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1036</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615784</v>
+        <v>615802</v>
       </c>
       <c r="R3" t="n">
         <v>6560219</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 43291-2024 artfynd.xlsx
+++ b/artfynd/A 43291-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
